--- a/outstandinglist.xlsx
+++ b/outstandinglist.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="7"/>
@@ -510,7 +510,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dr</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -530,12 +530,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2348070718766</t>
+          <t>2348164289106</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Dr</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Adebambo</t>
+          <t>Adaigbe</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dele</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>No 20 Sam Ogegbo Road</t>
+          <t>7 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2349153483352</t>
+          <t>2348070718766</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -585,27 +585,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Adegbite</t>
+          <t>Adebambo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Dele</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2 Sam Ogegbo Road</t>
+          <t>No 20 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2347059357158</t>
+          <t>2349153483352</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -620,27 +620,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Adegboye</t>
+          <t>Adegbite</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Adeniyi</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14 Jibewa Shomorin Close</t>
+          <t>2 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2348060227640</t>
+          <t>2347059357158</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>3,000</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ademoye </t>
+          <t>Adeoti</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Temitayo</t>
+          <t>David</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4 Martins Street</t>
+          <t>23 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2348067136212</t>
+          <t>2349038817804</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8,500</t>
+          <t>5,000</t>
         </is>
       </c>
     </row>
@@ -795,27 +795,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Adeniyi</t>
+          <t>Adetunji</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solomon </t>
+          <t>Adetayo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4 Martins Street</t>
+          <t>2 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2348067155887</t>
+          <t>2348163988888</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -830,20 +830,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Adetayo</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Olayinka</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2 Jibewa Shomorin Close</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>23A Jibewa Shomorin Close</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2348039691036</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>20,000</t>
@@ -861,12 +865,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Adetunji</t>
+          <t>Afolabi</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Olasumbo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -876,7 +880,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2348163988888</t>
+          <t>2348095056885</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -896,27 +900,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Ajila</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Olayinka</t>
+          <t>Ayo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23A Jibewa Shomorin Close</t>
+          <t>15 Victorious Avenue</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2348039691036</t>
+          <t>2348034828772</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>30,000</t>
         </is>
       </c>
     </row>
@@ -926,32 +930,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Afolabi</t>
+          <t>Ajisafe</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Kayode</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6 Jibewa Shomorin Close</t>
+          <t>2 Adeogun Street</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2348095056885</t>
+          <t>2348139987919</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -966,27 +970,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ajila</t>
+          <t>Akerele</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ayo</t>
+          <t>Saheed</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15 Victorious Avenue</t>
+          <t>13 Victorious Avenue</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2348034828772</t>
+          <t>2348174973527</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>12,000</t>
         </is>
       </c>
     </row>
@@ -996,32 +1000,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Alhaji </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Akerele</t>
+          <t>Akingbola</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Saheed</t>
+          <t>Bukky</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13 Victorious Avenue</t>
+          <t>14 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2348174973527</t>
+          <t>2348088396446</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>4,000</t>
         </is>
       </c>
     </row>
@@ -1031,32 +1035,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alhaji </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Akingbola</t>
+          <t xml:space="preserve">Amodu </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bukky</t>
+          <t>Abiodun</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14 Jibewa Shomorin Close</t>
+          <t>6 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2348088396446</t>
+          <t>2348022888195</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -1071,27 +1075,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Akpan</t>
+          <t>Andy</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sylvanus</t>
+          <t>Anyakpo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17 Jibewa Shomorin Close</t>
+          <t>7 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2348061699107</t>
+          <t>2348023416950</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>5,000</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1110,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ambali</t>
+          <t xml:space="preserve">Anusiem </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lekan</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5 Jibewa Shomorin Close</t>
+          <t>1 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2348034688604</t>
+          <t>2348030832515</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -1136,32 +1140,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amodu </t>
+          <t>Anyawu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Abiodun</t>
+          <t>Hilda</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6 Jibewa Shomorin Close</t>
+          <t>3 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2348022888195</t>
+          <t>2348034119127</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>4,000</t>
         </is>
       </c>
     </row>
@@ -1171,32 +1175,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Andy</t>
+          <t>Awoyemi</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Olusegun</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>7 Jibewa Shomorin Close</t>
+          <t>3 Victorious Avenue</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2348023416950</t>
+          <t>2348074736472</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>3,000</t>
         </is>
       </c>
     </row>
@@ -1206,32 +1210,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Anifowose A .O</t>
+          <t xml:space="preserve">Ayetemimowa </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Abiola</t>
+          <t>James</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23 Sam Ogegbo Road</t>
+          <t>5 Martins Street</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2348023421342</t>
+          <t>2349017630811</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -1241,32 +1245,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Mr </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anusiem </t>
+          <t>Azubike</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t xml:space="preserve">Samuel </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1 Sam Ogegbo Road</t>
+          <t>15 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2348030832515</t>
+          <t>2348165919773</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -1276,32 +1280,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Alhaji</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Anyawu</t>
+          <t xml:space="preserve">Baba </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hilda</t>
+          <t>Ibrahim</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3 Sam Ogegbo Road</t>
+          <t>13 Victorious Avenue</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2348034119127</t>
+          <t>2349132357459</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>30,000</t>
         </is>
       </c>
     </row>
@@ -1311,17 +1315,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mrs </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Asuquo</t>
+          <t>Babatunde</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elizabeth </t>
+          <t>Ibukun</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1331,12 +1335,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2348033381761</t>
+          <t>2348185177336</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>5,000</t>
         </is>
       </c>
     </row>
@@ -1351,27 +1355,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Awoyemi</t>
+          <t>Bamidele</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Olusegun</t>
+          <t>Olumide</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3 Victorious Avenue</t>
+          <t>7 Victorious Avenue</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2348074736472</t>
+          <t>2348032426997</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -1386,22 +1390,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ayetemimowa </t>
+          <t>Bayo</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Alabi</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5 Martins Street</t>
+          <t>18 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2349017630811</t>
+          <t>2347039534458</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1416,32 +1420,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azubike</t>
+          <t xml:space="preserve">Bethel </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samuel </t>
+          <t>College</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15 Sam Ogegbo Road</t>
+          <t>1 Victorious Avenue</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2348165919773</t>
+          <t>2349039175466</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>80,000</t>
         </is>
       </c>
     </row>
@@ -1451,27 +1455,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Alhaji</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baba </t>
+          <t>Bidemi</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ibrahim</t>
+          <t>Olayemi</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13 Victorious Avenue</t>
+          <t>7 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2349132357459</t>
+          <t>07039229295</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1491,27 +1495,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Babatunde</t>
+          <t>Celestina</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ibukun</t>
+          <t>Ruth</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2 Jibewa Shomorin Close</t>
+          <t>3 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2348185177336</t>
+          <t>2348082896410</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>2,200</t>
         </is>
       </c>
     </row>
@@ -1521,32 +1525,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bamidele</t>
+          <t>Comfort</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Olumide</t>
+          <t>Bendel House</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7 Victorious Avenue</t>
+          <t>20 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2348032426997</t>
+          <t>2348067050484</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -1561,27 +1565,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bayo</t>
+          <t>Dare</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Alabi</t>
+          <t>Adeogun</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>18 Jibewa Shomorin Close</t>
+          <t>2 Adeogun Street</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2347039534458</t>
+          <t>2348062105535</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -1596,27 +1600,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bethel </t>
+          <t>Ebo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>College</t>
+          <t>Kehinde</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1 Victorious Avenue</t>
+          <t>5 Victorious Avenue</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2349039175466</t>
+          <t>2348054283314</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -1626,32 +1630,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Blessing</t>
+          <t xml:space="preserve">Efemena </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Uba</t>
+          <t xml:space="preserve">Mavis </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20 Sam Ogegbo Road</t>
+          <t>3 Victorious Avenue</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2347064681113</t>
+          <t>2348063985093</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -1666,27 +1670,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Celestina</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ruth</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3 Sam Ogegbo Road</t>
+          <t>2 Adeogun Street</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2348082896410</t>
+          <t>2347064439966</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -1701,27 +1705,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dare</t>
+          <t>Enaholo</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Adeogun</t>
+          <t>David</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>4 Martins Street</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2348062105535</t>
+          <t>2348134694901</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>3,000</t>
         </is>
       </c>
     </row>
@@ -1731,27 +1735,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Ms</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Eniayekan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Precious</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>23 Sam Ogegbo Road</t>
+          <t>11 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2349038817804</t>
+          <t>2348181008962</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1766,32 +1770,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Ms</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ebo</t>
+          <t xml:space="preserve">Enumah </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Kehinde</t>
+          <t>Faith</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5 Victorious Avenue</t>
+          <t>20 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2348054283314</t>
+          <t>2349060884030</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>4,000</t>
         </is>
       </c>
     </row>
@@ -1801,32 +1805,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Dcns</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Efemena </t>
+          <t>Esther</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mavis </t>
+          <t>Osarodion</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3 Victorious Avenue</t>
+          <t>20 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2348063985093</t>
+          <t>2348034011995</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>14,000</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1845,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Godwin</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Nwosu</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>15 Olanpejo Street</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2347064439966</t>
+          <t>2348030964175</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1876,27 +1880,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Enaholo</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Ani</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4 Martins Street</t>
+          <t>5 Victorious Avenue</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2348134694901</t>
+          <t>2347037603628</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -1906,27 +1910,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ms</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eniayekan</t>
+          <t xml:space="preserve">Ibukun </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Precious</t>
+          <t>Akintade</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11 Jibewa Shomorin Close</t>
+          <t>1 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2348181008962</t>
+          <t>2348074088887</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1941,32 +1945,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ms</t>
+          <t>Ms.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enumah </t>
+          <t>Ifeoma</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Faith</t>
+          <t>Emeka</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20 Sam Ogegbo Road</t>
+          <t>No 3 Martins Street</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2349060884030</t>
+          <t>2349154628676</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>12,000</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1980,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dcns</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Esther</t>
+          <t>Igwillo</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Osarodion</t>
+          <t xml:space="preserve">Clinton </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20 Sam Ogegbo Road</t>
+          <t>5 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2348034011995</t>
+          <t>2348038588597</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>2,200</t>
         </is>
       </c>
     </row>
@@ -2011,32 +2015,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Ms.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Etim</t>
+          <t>Iheoma</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Berryl</t>
+          <t>c/o Igwe</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16 Sam Ogegbo Road</t>
+          <t>3 Martins Street</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2348028591146</t>
+          <t>2347035304920</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>12,000</t>
         </is>
       </c>
     </row>
@@ -2051,27 +2055,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Godwin</t>
+          <t>Jaywon</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Nwosu</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>15 Olanpejo Street</t>
+          <t>18 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2348030964175</t>
+          <t>2349068400154</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>2,000</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2085,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Ms.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hassan</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Yinusa</t>
+          <t>Ginka</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>18 Sam Ogegbo Road</t>
+          <t>2 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2349079864312</t>
+          <t>2348089953097</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -2116,27 +2120,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Mr </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Jesutobi</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ani</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>5 Victorious Avenue</t>
+          <t>23 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2347037603628</t>
+          <t>2348057387415</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2156,12 +2160,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ibukun </t>
+          <t xml:space="preserve">Joel </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Akintade</t>
+          <t>Ogboji</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2171,7 +2175,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2348074088887</t>
+          <t>2349065571043</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2186,32 +2190,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ms.</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ifeoma</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Emeka</t>
+          <t>Obinna</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>No 3 Martins Street</t>
+          <t>13 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2349154628676</t>
+          <t>2348137343312</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -2226,27 +2230,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Igwe</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Kelechi</t>
+          <t>Opeyemi</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20 Jibewa Shomorin Close</t>
+          <t>3 Victorious Avenue</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2348022897987</t>
+          <t>2348033869066</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -2261,27 +2265,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Igwillo</t>
+          <t>Kayode</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinton </t>
+          <t>Olanbiwonninum</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5 Jibewa Shomorin Close</t>
+          <t>6 Martins Street</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2348038588597</t>
+          <t>2348130853892</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>7,000</t>
         </is>
       </c>
     </row>
@@ -2291,32 +2295,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ms.</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iheoma</t>
+          <t>Lawal</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>c/o Igwe</t>
+          <t>Adedolapo</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>No 3 Martins Street Victory Estate</t>
+          <t>11 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2347035304920</t>
+          <t>2347063861766</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -2331,27 +2335,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jaywon</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t xml:space="preserve"> Treasure </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>18 Sam Ogegbo Road</t>
+          <t>6 Olanpejo Street</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2349068400154</t>
+          <t>2348057105540</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>6,000</t>
         </is>
       </c>
     </row>
@@ -2361,27 +2365,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ms.</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t xml:space="preserve">Makyeni </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ginka</t>
+          <t xml:space="preserve">Anthony </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2 Jibewa Shomorin Close</t>
+          <t>5 Martins Street</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2348089953097</t>
+          <t>2348130779792</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2396,12 +2400,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jesutobi</t>
+          <t>Maxwell</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2411,12 +2415,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>23 Sam Ogegbo Road</t>
+          <t>7 Victorious Avenue</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2348057387415</t>
+          <t>2347053863557</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2436,12 +2440,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joel </t>
+          <t xml:space="preserve">Morayo </t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ogboji</t>
+          <t>Akinsanya</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2451,7 +2455,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2349065571043</t>
+          <t>2348144455816</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2471,27 +2475,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Nifemi</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Obinna</t>
+          <t>Eitaio</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>13 Sam Ogegbo Road</t>
+          <t>11 Victorious Avenue</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2348137343312</t>
+          <t>447411592514</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>4,000</t>
         </is>
       </c>
     </row>
@@ -2501,32 +2505,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kayode</t>
+          <t>Nkechinyere</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Olanbiwonninum</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>6 Martins Street</t>
+          <t>3 Sam Ogegbo Street</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2348130853892</t>
+          <t>2349026789985</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -2536,27 +2540,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lawal</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Adedolapo</t>
+          <t>Aderemi</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>11 Jibewa Shomorin Close</t>
+          <t>9 Martins Street</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2347063861766</t>
+          <t>2347035699285</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2576,27 +2580,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lawal </t>
+          <t>Nwanneka</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Halima</t>
+          <t>Blessesd</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1 Adeogun Street</t>
+          <t>5 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2348037327170</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -2606,32 +2610,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Ms.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t xml:space="preserve">Odubanjo </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Treasure </t>
+          <t>Eniola</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>6 Olanpejo Street</t>
+          <t>1 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2348057105540</t>
+          <t>2348138046673</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -2646,27 +2650,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Makyeni </t>
+          <t>Ogbonna</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anthony </t>
+          <t>Kelechi</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>5 Martins Street</t>
+          <t>15 Olanpejo Street</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2348130779792</t>
+          <t>2348033623568</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>30,000</t>
         </is>
       </c>
     </row>
@@ -2681,22 +2685,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mattew</t>
+          <t xml:space="preserve">Oguche </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Emmanuel</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>23B Jibewa Shomorin Close</t>
+          <t>1 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2348032019300</t>
+          <t>2348087423235</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2711,27 +2715,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Mr </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Maxwell</t>
+          <t>Ogunjana</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Femi</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>7 Victorious Avenue</t>
+          <t>3 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2347053863557</t>
+          <t>2348028538923</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2751,12 +2755,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morayo </t>
+          <t>Ojo</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Akinsanya</t>
+          <t xml:space="preserve">Temilade </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2766,7 +2770,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2348144455816</t>
+          <t>2347030587940</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2786,27 +2790,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nifemi</t>
+          <t>Olajide</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Eitaio</t>
+          <t>Bakare</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>11 Victorious Avenue</t>
+          <t>1 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>447411592514</t>
+          <t>2348028593550</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -2821,27 +2825,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nkechinyere</t>
+          <t>Olalekan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Sakirat</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>3 Sam Ogegbo Street Victory estate</t>
+          <t>6 Martins Street</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2349026789985</t>
+          <t>2349124065368</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>7,000</t>
         </is>
       </c>
     </row>
@@ -2851,27 +2855,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Olalekan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Aderemi</t>
+          <t>Otunba</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>9 Martins Street</t>
+          <t>17 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2347035699285</t>
+          <t>2348182300274</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2886,32 +2890,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nwanneka</t>
+          <t xml:space="preserve">Olanpejo </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Blessesd</t>
+          <t xml:space="preserve">Baba Tawa </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>5 Jibewa Shomorin Close</t>
+          <t>7 Olanpejo Street</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2348037327170</t>
+          <t>2348029083918</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>2,000</t>
         </is>
       </c>
     </row>
@@ -2926,22 +2930,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Odiana</t>
+          <t>Oluwole</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Soltune</t>
+          <t>Segun</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11 Jibewa Shomorin Close</t>
+          <t>17 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2348138146320</t>
+          <t>2348062083632</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2956,32 +2960,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mrs </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odoguwa </t>
+          <t>Omoruyi</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Olusola</t>
+          <t>Augustine</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>19 Sam Ogegbo Road</t>
+          <t>17 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2348023431044</t>
+          <t>2348134612833</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -2991,27 +2995,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ms.</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odubanjo </t>
+          <t>Omotayo</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Eniola</t>
+          <t>Christopher</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1 Sam Ogegbo Road</t>
+          <t>19 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2348138046673</t>
+          <t>2348023260295</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3026,27 +3030,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Odukoya</t>
+          <t>Omowumi</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Oluwatobi</t>
+          <t>Ojo</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>7 Victorious Avenue</t>
+          <t>1 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2348182024906</t>
+          <t>2348185103553</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3066,27 +3070,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ogbonna</t>
+          <t>Onyeukwu</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Kelechi</t>
+          <t xml:space="preserve">Ikechukwu </t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>15 Olanpejo Street</t>
+          <t>18 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2348033623568</t>
+          <t>2348036295974</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -3096,27 +3100,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Miss </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oguche </t>
+          <t>Osuji</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Emmanuel</t>
+          <t>Ezinne</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1 Sam Ogegbo Road</t>
+          <t>25 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2348087423235</t>
+          <t>2348068947962</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3131,27 +3135,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ogunjana</t>
+          <t xml:space="preserve">Owotoke </t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Femi</t>
+          <t xml:space="preserve">Makanjuola </t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>3 Sam Ogegbo Road</t>
+          <t>1 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2348028538923</t>
+          <t>2347068768665</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3166,32 +3170,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baba </t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ogunjirin</t>
+          <t>Oyefia</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tunde</t>
+          <t>Frebe</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>9 Jibewa Shomorin Close</t>
+          <t>9 Olanpejo Street</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2348032400317</t>
+          <t>2348038510658</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -3206,27 +3210,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ojo</t>
+          <t>Oyemah</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temilade </t>
+          <t>Hope</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1 Sam Ogegbo Road</t>
+          <t>21 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2347030587940</t>
+          <t>2348153992720</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>18,000</t>
         </is>
       </c>
     </row>
@@ -3236,27 +3240,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elder </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ojomu</t>
+          <t>Oyesanya</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Segun</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>8 Jibewa Shomorin Close</t>
+          <t>11 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2348033253879</t>
+          <t>2347057656588</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3276,27 +3280,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Olajide</t>
+          <t xml:space="preserve">Pali </t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Bakare</t>
+          <t>Agro</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1 Sam Ogegbo Road</t>
+          <t>12 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2348028593550</t>
+          <t>2349019622092</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>80,000</t>
         </is>
       </c>
     </row>
@@ -3306,32 +3310,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Olalekan</t>
+          <t xml:space="preserve">Phillip </t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sakirat</t>
+          <t>ThankGod</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>6 Martins Street</t>
+          <t>8 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2349124065368</t>
+          <t>2349064090986</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -3346,22 +3350,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Olalekan</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Otunba</t>
+          <t>Chidiebere</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>17 Jibewa Shomorin Close</t>
+          <t>7 Victorious Avenue</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2348182300274</t>
+          <t>2348030804988</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3376,32 +3380,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Mr </t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olanpejo </t>
+          <t>Segun</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baba Tawa </t>
+          <t>na</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>7 Olanpejo Street</t>
+          <t>25 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2348029083918</t>
+          <t>2348035397317</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -3416,27 +3420,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oluwole</t>
+          <t>Seme</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Segun</t>
+          <t>Agbara</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17 Jibewa Shomorin Close</t>
+          <t>8 Martins Street</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2348062083632</t>
+          <t>2348028184383</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>40,000</t>
         </is>
       </c>
     </row>
@@ -3451,27 +3455,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Omoruyi</t>
+          <t>Seyi</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Augustine</t>
+          <t>Freddie</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>17 Jibewa Shomorin Close</t>
+          <t>24 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2348134612833</t>
+          <t>41797811526</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -3486,27 +3490,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Omotayo</t>
+          <t>Sir Tailor</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Christopher</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>19 Jibewa Shomorin Close</t>
+          <t>2 Adeogun Street</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2348023260295</t>
+          <t>2348064658198</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -3516,32 +3520,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Omowumi</t>
+          <t>Sola</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Ojo</t>
+          <t>Folowosele</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1 Sam Ogegbo Road</t>
+          <t>No7 Olanpejo Street Victory Estate</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2348185103553</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>30,000</t>
         </is>
       </c>
     </row>
@@ -3556,27 +3560,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Onyeukwu</t>
+          <t>Sola</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ikechukwu </t>
+          <t>Folowosele</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>18 Jibewa Shomorin Close</t>
+          <t>No7 Olanpejo Street Victory Estate</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2348036295974</t>
+          <t>+234 8034102329</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>30,000</t>
         </is>
       </c>
     </row>
@@ -3586,32 +3590,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miss </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Osuji</t>
+          <t>Sola</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ezinne</t>
+          <t>Folowosele</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>25 Jibewa Shomorin Close</t>
+          <t>No7 Olanpejo Street Victory Estate</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2348068947962</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>30,000</t>
         </is>
       </c>
     </row>
@@ -3626,27 +3630,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owotoke </t>
+          <t xml:space="preserve">Solomon </t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Makanjuola </t>
+          <t xml:space="preserve">Wuike </t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1 Sam Ogegbo Road</t>
+          <t>7 Martins Street</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2347068768665</t>
+          <t>2348060221829</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>15,000</t>
         </is>
       </c>
     </row>
@@ -3656,32 +3660,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Oyefia</t>
+          <t>Tajudeen</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Frebe</t>
+          <t>Ojo</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>9 Olanpejo Street</t>
+          <t>6 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2348038510658</t>
+          <t>2348023181917</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -3691,32 +3695,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Mr </t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Oyemah</t>
+          <t>Tomisin</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Hope</t>
+          <t>Obakpolo</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>21 Sam Ogegbo Road</t>
+          <t>7 Martins Street</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2348153992720</t>
+          <t>2349084860718</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>5,200</t>
         </is>
       </c>
     </row>
@@ -3726,32 +3730,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Oyesanya</t>
+          <t>Ufele</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Segun</t>
+          <t>Tochukwu</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>11 Jibewa Shomorin Close</t>
+          <t>20 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2347057656588</t>
+          <t>2348036912727</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>10,000</t>
         </is>
       </c>
     </row>
@@ -3761,32 +3765,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pali </t>
+          <t>Ukaha</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Agro</t>
+          <t>Eberechi</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>12 Sam Ogegbo Road</t>
+          <t>16 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2349019622092</t>
+          <t>2348064383418</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>3,000</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3800,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Engrn</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phillip </t>
+          <t>Wabara</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ThankGod</t>
+          <t>Chinedu</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>8 Sam Ogegbo Road</t>
+          <t>5 Victorious Avenue</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2349064090986</t>
+          <t>2348188276133</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>40,000</t>
         </is>
       </c>
     </row>
@@ -3836,585 +3840,25 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t xml:space="preserve">Wale </t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Chidiebere</t>
+          <t>Akinwunmi</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>7 Victorious Avenue</t>
+          <t>8 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2348030804988</t>
+          <t>2349098037363</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>97</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mr </t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Segun</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>25 Jibewa Shomorin Close</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2348035397317</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="1" t="n">
-        <v>98</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Seme</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Agbara</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>8 Martins Street</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2348028184383</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>40,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Seyi</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Freddie</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>24 Jibewa Shomorin Close</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>41797811526</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Sir Tailor</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>2 Adeogun Street</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2348064658198</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="1" t="n">
-        <v>101</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Siyaka</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Henry</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>24 Jibewa Shomorin Close</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2348024790662</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="n">
-        <v>102</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Soji</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Adeogun</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>2 Adeogun Street</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2348158941240</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solomon </t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wuike </t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>7 Martins Street</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2348060221829</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>15,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mr </t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Tajudeen</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Adebayo</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>6 Jibewa Shomorin Close</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2348023181917</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tolulope </t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Akinjise</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>23 Sam Ogegbo Road</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2348169696476</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mr </t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Tomisin</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Obakpolo</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>7 Martins Street</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2349084860718</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>5,200</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="1" t="n">
-        <v>107</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Mrs</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Ufele</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Tochukwu</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>20 Sam Ogegbo Road</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2348036912727</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Mrs</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Ukaha</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Eberechi</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>16 Sam Ogegbo Road</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2348064383418</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>8,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="n">
-        <v>109</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Ututu</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Cletus</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>8 Sam Ogegbo Road</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2348039727477</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>5,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="n">
-        <v>110</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Engrn</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Wabara</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Chinedu</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>5 Victorious Avenue</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2348188276133</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>40,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="1" t="n">
-        <v>111</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wale </t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Akinwunmi</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>8 Sam Ogegbo Road</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2349098037363</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>15,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="1" t="n">
-        <v>112</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mr </t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Yinka</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>7 Martins Street</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2348034709952</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
         <is>
           <t>15,000</t>
         </is>
